--- a/Content_Calendar.xlsx
+++ b/Content_Calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John\Desktop\content calendar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8679989-700A-402E-B4AA-6246D78F7734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7891210E-2699-4F0C-9E88-6150910EBABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{FA463503-EEA9-4E36-AF77-605EC82561F6}"/>
   </bookViews>
@@ -335,9 +335,6 @@
     <t>This is Chita. She is 8 years old and lives in Cambodia. \n\n📸 We gave her a camera and asked her to take a picture of what she finds beautiful in the world. Chita decided to take a picture of the “kontout” fruit tree.\n\nShe said, “I photographed this tree because the fruit tastes very good. Sweet and sour. I like them.”\n\nLet’s not forget the beauty that surrounds us everyday. Let’s see the world like Chita does.</t>
   </si>
   <si>
-    <t>When you think of the perfect Christmas gift, you may not think of chickens.\n\nBut you might when you hear Betty and Michal’s inspiring story.\n\n“Now we can be sure to eat two meals a day. We have enough money to buy food. My children are healthy,” Betty says. 🙏 \n\nIsn’t that beautiful? \n\nBefore someone caring made room for gifts of love, their family struggled with hunger and uncertainty. Everything changed when someone like you sent chickens and seeds that helped them grow food, earn income and dream again.\n\nYou can help another family put food on the table now and for years to come.\n\nShop the Gift Catalog online &gt; www.fh.org/shop</t>
-  </si>
-  <si>
     <t>“My children were malnourished and we hardly ate one meal a day,” says Betty in Uganda. \n\nBetty and Michal struggled to feed their daughters and pay school fees. But everything changed when kind people like you helped change their lives with gifts from the Food for the Hungry Gift Catalog. \n \n Chickens to lay eggs. Seeds to grow vegetables. Tools and training to build a future. \n \n “Now we eat two meals a day. My children are healthy. We have hope,” Betty shares. 🫶 \n\nThis Christmas, you can give a gift that puts food on the table and changes lives.</t>
   </si>
   <si>
@@ -548,6 +545,9 @@
   </si>
   <si>
     <t>Grateful for the incredible community and church leaders coming together as Church of the City in Franklin, Tennessee has been building powerful partnership with the community of La Cuneta in the Dominican Republic. \n\n  Excited for the journey ahead as we work hand in hand to bring hope, love, and lasting impact!</t>
+  </si>
+  <si>
+    <t>When you think of the perfect Christmas gift, you may not think of chickens.\n\nBut you might when you hear Betty and Michal’s inspiring story.\n\n“Now we can be sure to eat two meals a day. We have enough money to buy food. My children are healthy,” Betty says. 🙏 \n\nIsn’t that beautiful? \n\nBefore someone caring made room for gifts of love, their family struggled with hunger and uncertainty. Everything changed when someone like you sent chickens and seeds that helped them grow food, earn income and dream again.\n\nYou can help another family put food on the table now and for years to come.</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1066,7 @@
         <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>22</v>
@@ -1105,7 +1105,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>20</v>
@@ -1114,7 +1114,7 @@
         <v>27</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>22</v>
@@ -1159,10 +1159,10 @@
         <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>22</v>
@@ -1189,7 +1189,7 @@
         <v>23</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="105" x14ac:dyDescent="0.25">
@@ -1258,7 +1258,7 @@
         <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>22</v>
@@ -1402,7 +1402,7 @@
         <v>43</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>22</v>
@@ -1573,10 +1573,10 @@
         <v>23</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="120" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>20</v>
@@ -1594,7 +1594,7 @@
         <v>53</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>22</v>
@@ -1681,7 +1681,7 @@
         <v>26</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>20</v>
@@ -1731,10 +1731,10 @@
         <v>20</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>22</v>
@@ -1779,10 +1779,10 @@
         <v>20</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>22</v>
@@ -1809,7 +1809,7 @@
         <v>23</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -1869,7 +1869,7 @@
         <v>26</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>20</v>
@@ -1878,7 +1878,7 @@
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>22</v>
@@ -1917,16 +1917,16 @@
         <v>26</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>22</v>
@@ -1974,7 +1974,7 @@
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>22</v>
@@ -2001,7 +2001,7 @@
         <v>23</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="135" x14ac:dyDescent="0.25">
@@ -2022,7 +2022,7 @@
         <v>72</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>22</v>
@@ -2037,10 +2037,10 @@
         <v>23</v>
       </c>
       <c r="N22" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>23</v>
@@ -2070,7 +2070,7 @@
         <v>21</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>22</v>
@@ -2118,7 +2118,7 @@
         <v>31</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>22</v>
@@ -2136,7 +2136,7 @@
         <v>57</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>23</v>
@@ -2163,10 +2163,10 @@
         <v>20</v>
       </c>
       <c r="F25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>22</v>
@@ -2193,7 +2193,7 @@
         <v>23</v>
       </c>
       <c r="R25" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="45" x14ac:dyDescent="0.25">
@@ -2262,7 +2262,7 @@
         <v>84</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>22</v>
@@ -2310,7 +2310,7 @@
         <v>33</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>22</v>
@@ -2358,7 +2358,7 @@
         <v>43</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>22</v>
@@ -2406,7 +2406,7 @@
         <v>53</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>22</v>
@@ -2492,16 +2492,16 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
         <v>20</v>
       </c>
       <c r="F32" t="s">
+        <v>132</v>
+      </c>
+      <c r="G32" t="s">
         <v>133</v>
-      </c>
-      <c r="G32" t="s">
-        <v>134</v>
       </c>
       <c r="H32" t="s">
         <v>22</v>
@@ -2525,7 +2525,7 @@
         <v>23</v>
       </c>
       <c r="R32" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -2536,16 +2536,16 @@
         <v>26</v>
       </c>
       <c r="D33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" t="s">
         <v>136</v>
       </c>
-      <c r="E33" t="s">
-        <v>20</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>137</v>
-      </c>
-      <c r="G33" t="s">
-        <v>138</v>
       </c>
       <c r="H33" t="s">
         <v>22</v>
@@ -2569,7 +2569,7 @@
         <v>23</v>
       </c>
       <c r="R33" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -2580,16 +2580,16 @@
         <v>26</v>
       </c>
       <c r="D34" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" t="s">
         <v>140</v>
       </c>
-      <c r="E34" t="s">
-        <v>20</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>141</v>
-      </c>
-      <c r="G34" t="s">
-        <v>142</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
@@ -2613,7 +2613,7 @@
         <v>23</v>
       </c>
       <c r="R34" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -2624,16 +2624,16 @@
         <v>26</v>
       </c>
       <c r="D35" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" t="s">
+        <v>162</v>
+      </c>
+      <c r="G35" t="s">
         <v>144</v>
-      </c>
-      <c r="E35" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35" t="s">
-        <v>163</v>
-      </c>
-      <c r="G35" t="s">
-        <v>145</v>
       </c>
       <c r="H35" t="s">
         <v>22</v>
@@ -2657,7 +2657,7 @@
         <v>23</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -2668,16 +2668,16 @@
         <v>26</v>
       </c>
       <c r="D36" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" t="s">
         <v>147</v>
       </c>
-      <c r="E36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>148</v>
-      </c>
-      <c r="G36" t="s">
-        <v>149</v>
       </c>
       <c r="H36" t="s">
         <v>22</v>
@@ -2701,7 +2701,7 @@
         <v>23</v>
       </c>
       <c r="R36" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -2712,16 +2712,16 @@
         <v>26</v>
       </c>
       <c r="D37" t="s">
+        <v>150</v>
+      </c>
+      <c r="E37" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" t="s">
         <v>151</v>
       </c>
-      <c r="E37" t="s">
-        <v>20</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>152</v>
-      </c>
-      <c r="G37" t="s">
-        <v>153</v>
       </c>
       <c r="H37" t="s">
         <v>22</v>
@@ -2745,7 +2745,7 @@
         <v>23</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -2756,16 +2756,16 @@
         <v>26</v>
       </c>
       <c r="D38" t="s">
+        <v>154</v>
+      </c>
+      <c r="E38" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" t="s">
         <v>155</v>
       </c>
-      <c r="E38" t="s">
-        <v>20</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>156</v>
-      </c>
-      <c r="G38" t="s">
-        <v>157</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
@@ -2777,7 +2777,7 @@
         <v>22</v>
       </c>
       <c r="N38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O38" t="s">
         <v>58</v>
@@ -2800,16 +2800,16 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" t="s">
         <v>158</v>
       </c>
-      <c r="E39" t="s">
-        <v>20</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>159</v>
-      </c>
-      <c r="G39" t="s">
-        <v>160</v>
       </c>
       <c r="H39" t="s">
         <v>22</v>
@@ -2833,7 +2833,7 @@
         <v>23</v>
       </c>
       <c r="R39" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -2844,16 +2844,16 @@
         <v>26</v>
       </c>
       <c r="D40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E40" t="s">
         <v>20</v>
       </c>
       <c r="F40" t="s">
+        <v>165</v>
+      </c>
+      <c r="G40" t="s">
         <v>166</v>
-      </c>
-      <c r="G40" t="s">
-        <v>167</v>
       </c>
       <c r="H40" t="s">
         <v>22</v>
@@ -2878,7 +2878,7 @@
         <v>23</v>
       </c>
       <c r="R40" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/Content_Calendar.xlsx
+++ b/Content_Calendar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fhorg.sharepoint.com/sites/msteams_26c5e1_626896/Shared Documents/Offers, Experience &amp; Retention/FH Impact Mobile App/Investor Mobile App - Content Feeds/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E7E0073-3221-4D86-BEE3-126FE8D7E62E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20258F96-3EBF-405E-A52A-478AD36ACDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="35550" windowHeight="15330" xr2:uid="{FA463503-EEA9-4E36-AF77-605EC82561F6}"/>
   </bookViews>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="300">
   <si>
     <t>Category</t>
   </si>
@@ -240,7 +240,7 @@
     <t>A Christmas Prayer🙏</t>
   </si>
   <si>
-    <t>Heavenly Father, /n/nThank you for the gift of your Son, Jesus, who brings hope, joy, and light to our world. This Christmas, I pray for children and families around the globe who are facing big challenges. May they experience your love in tangible ways—through warm meals, safe homes, opportunities to learn, and the care of those who support them. /n/nBless my sponsored child and every child in these communities with a heart full of joy. May the hope of Christ’s birth, His promises, and His presence shine brightly in their lives. /n/nThank you for stirring up generosity and using us to help children build the futures you intend for them.  Help me reflect your love in everything I do this season. In Jesus’ name, amen.</t>
+    <t>Heavenly Father, /n/nThank you for the gift of your Son, Jesus, who brings hope, joy, and light to our world. This Christmas, I pray for children and families around the globe who are facing big challenges. May they experience your love in tangible ways—through warm meals, safe homes, opportunities to learn, and the care of those who support them. /n/nBless my sponsored child and every child in these communities with a heart full of joy. May the hope of Christ’s birth, His promises, and His presence shine brightly in their lives. /n/n Thank you for stirring up generosity and using us to help children build the futures you intend for them.  Help me reflect your love in everything I do this season. In Jesus’ name, amen.</t>
   </si>
   <si>
     <t>About FH</t>
@@ -997,6 +997,118 @@
   </si>
   <si>
     <t>https://www.facebook.com/foodforthehungry/posts/pfbid0mc5BKcUwn5yGgkdG7kpK95YDLUGh6dwD6PrKuS7a6DjXijg5Rup3upWxCjHrZgCCl</t>
+  </si>
+  <si>
+    <t>Org_WASH_July01</t>
+  </si>
+  <si>
+    <t>Before, Life Was Quite Difficult</t>
+  </si>
+  <si>
+    <t>Dirty water meant disease. \n\n
+❌ Her children were constantly sick.\n
+❌ They walked 2 kilometers just to collect unsafe water.\n
+❌ School was missed. Hygiene suffered. Hope felt far away.\n
+Today, clean water is just steps from her home. 🙌\n\n
+“Our children are now attending school… Our sanitation has tremendously improved… Water-related diseases have also significantly declined.” 
+This is the difference clean water makes. 💧💧💧</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid05mqn39BPCzHCQCHtoKMq3T4Vyk8qxobzKvgYYpKWpNS9dJ3yAVAvXbHufCV2oXzgl</t>
+  </si>
+  <si>
+    <t>Org_Greeting_July03</t>
+  </si>
+  <si>
+    <t>Happy Friday from Cambodia!</t>
+  </si>
+  <si>
+    <t>Org_Education_July07</t>
+  </si>
+  <si>
+    <t>Increasing Literacy Through Partnership</t>
+  </si>
+  <si>
+    <t>“…me and my friends use to spend our free time [after] school to play, now we are coming to study and read books together.”\n\n
+10-year-old Hoo from Cambodia is improving her literacy skills by having access to a new library in her community. Food for the Hungry staff met with community leaders to come up with ways to encourage children to read more. \n\n
+After the meeting, village leaders and parents worked together to build a library for the community and volunteer teachers set up the library with books donated by Food for the Hungry. Now, nearly 60 out of 80 children come to the library to read and learn more!</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid05EAtTbwqpSsx1Z4ofHZrQyeexDToFHs9tzaiQ6mi8rpZTGEYiamFt1hLTNYfGMTbl</t>
+  </si>
+  <si>
+    <t>Org_Impact_July11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irene’s Story Will Inspire You! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">She’s president of her community kitchen, the Olla Común, runs a successful mototaxi business, and has this message for other moms: “Value yourselves. Help your children become professionals, independent, and hardworking. Don’t give up.” 
+</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid0355KhWk1mktkwwapsQwEqVTG2oK3P3AP4hHAb11WzTGYJjfY3s9sywKEJjdJWgkKEl</t>
+  </si>
+  <si>
+    <t>Org_Education_July15</t>
+  </si>
+  <si>
+    <t>Your destiny is not written—you can write it</t>
+  </si>
+  <si>
+    <t>Melisio, a 17-year-old from Peru, always dreamed of becoming a scientist, fueled by his passion for discovery and helping others. With limited resources and few career opportunities in his community, pursuing higher education seemed impossible. But through Food for the Hungry Peru, he gained the guidance and support needed to turn his dreams into reality.</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid0hR5cagCQ9qH5QZNR1dFGbagrFCwneJsVoYBPaGhbf7C6vk2YnTHbPurJDYJ8e6Anl</t>
+  </si>
+  <si>
+    <t>Org_Impact_July20</t>
+  </si>
+  <si>
+    <t>Give the Chance to Learn and Move Forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Sometimes I was late, and sometimes I stayed home for weeks."
+For Nit Nim, getting to school wasn't easy. Without transportation, she often missed classes and fell behind.\n\n
+Then she received a bicycle.\n\n
+"Receiving a bicycle changed everything. Now I am never late. I learn every day and study values and knowledge at the pagoda."\n\n
+Today, Nit Nim attends school consistently, is thriving in her studies, and is dreaming about the future.\n\n
+"I believe education will change my future. One day, I dream of opening my own clothing shop."\n\n
+Thank you for helping children like Nit Nim move forward with hope, opportunity, and the chance to learn.\n\n
+</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid025sfBkgZBnk7fTR3VzafRpousS8JaSQ9HtiYry13J6u1VfXxwepgHzhhpBV39pxQal</t>
+  </si>
+  <si>
+    <t>Org_Hope_July24</t>
+  </si>
+  <si>
+    <t>Small Tools Can Inspire Big Dreams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Bangladesh, we recently distributed HOPE Kits to 18,000 children across five Area Programs, providing learning materials and pens to support their educational journey.\n\n
+✏️And, 120 students participated in a Drawing, Book Reading, and Essay Writing Competition designed to encourage creativity, build confidence, strengthen reading habits, and create opportunities for learning and connection. \n\n
+Every child deserves the opportunity to learn, grow, and dream about what comes next. </t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid02ZrXDfZZFCg37LNPYsVNqcaagzMz6X7Wzu9bZkYz7renK2iPzTSpGqnVJckYVDfzPl</t>
+  </si>
+  <si>
+    <t>Org_Impact_July28</t>
+  </si>
+  <si>
+    <t>Practical Programs Which Make a Difference</t>
+  </si>
+  <si>
+    <t>For years, Amina worried about how she would feed her children and keep them in school.\n\n
+Then she participated in Food for the Hungry's animal husbandry training and received a goat. She worked hard, grew her herd from one goat to seven, and made a bold decision to sell four goats to purchase a donkey and cart for a transportation business.\n\n
+Today, her family has moved from daily survival to stability and growth.\n\n
+"I am earning a better income now, and my children enjoy fresh goat's milk every day," Amina says. "I am so thankful to Food for the Hungry for this wonderful transformation and for solving my family's basic nutritional needs."\n\n
+What started as one opportunity became a pathway to stability, nutrition, and hope for her children.</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid0uJLRMjbyuVVgoP4gw9guTvYCn2A9R4DyZYnwucrLanjJ9FMRBg1pjLT6c1MzqP34l</t>
   </si>
 </sst>
 </file>
@@ -1543,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5370A7A5-E4F2-4D3A-BFE4-977B55C8323A}">
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="19.5703125" customWidth="1"/>
@@ -4382,6 +4494,353 @@
       </c>
       <c r="R62" s="8" t="s">
         <v>269</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="109.5">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>270</v>
+      </c>
+      <c r="E63" t="s">
+        <v>21</v>
+      </c>
+      <c r="F63" t="s">
+        <v>271</v>
+      </c>
+      <c r="G63" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="H63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J63" s="9">
+        <v>46204</v>
+      </c>
+      <c r="M63" t="s">
+        <v>27</v>
+      </c>
+      <c r="N63" t="s">
+        <v>32</v>
+      </c>
+      <c r="O63" t="s">
+        <v>32</v>
+      </c>
+      <c r="P63" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>27</v>
+      </c>
+      <c r="R63" s="8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="16.5">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" t="s">
+        <v>210</v>
+      </c>
+      <c r="D64" t="s">
+        <v>274</v>
+      </c>
+      <c r="E64" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="G64" s="14"/>
+      <c r="H64" t="s">
+        <v>24</v>
+      </c>
+      <c r="J64" s="9">
+        <v>46206</v>
+      </c>
+      <c r="M64" t="s">
+        <v>27</v>
+      </c>
+      <c r="N64" t="s">
+        <v>32</v>
+      </c>
+      <c r="O64" t="s">
+        <v>32</v>
+      </c>
+      <c r="P64" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="72.75">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" t="s">
+        <v>276</v>
+      </c>
+      <c r="E65" t="s">
+        <v>21</v>
+      </c>
+      <c r="F65" t="s">
+        <v>277</v>
+      </c>
+      <c r="G65" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="H65" t="s">
+        <v>24</v>
+      </c>
+      <c r="J65" s="9">
+        <v>46210</v>
+      </c>
+      <c r="M65" t="s">
+        <v>27</v>
+      </c>
+      <c r="N65" t="s">
+        <v>32</v>
+      </c>
+      <c r="O65" t="s">
+        <v>32</v>
+      </c>
+      <c r="P65" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>27</v>
+      </c>
+      <c r="R65" s="8" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="43.5">
+      <c r="A66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" t="s">
+        <v>280</v>
+      </c>
+      <c r="E66" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" t="s">
+        <v>281</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="H66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J66" s="9">
+        <v>46214</v>
+      </c>
+      <c r="M66" t="s">
+        <v>27</v>
+      </c>
+      <c r="N66" t="s">
+        <v>32</v>
+      </c>
+      <c r="O66" t="s">
+        <v>32</v>
+      </c>
+      <c r="P66" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>27</v>
+      </c>
+      <c r="R66" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
+      <c r="A67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" t="s">
+        <v>284</v>
+      </c>
+      <c r="E67" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" t="s">
+        <v>285</v>
+      </c>
+      <c r="G67" t="s">
+        <v>286</v>
+      </c>
+      <c r="H67" t="s">
+        <v>24</v>
+      </c>
+      <c r="J67" s="9">
+        <v>46218</v>
+      </c>
+      <c r="M67" t="s">
+        <v>27</v>
+      </c>
+      <c r="N67" t="s">
+        <v>32</v>
+      </c>
+      <c r="O67" t="s">
+        <v>32</v>
+      </c>
+      <c r="P67" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>27</v>
+      </c>
+      <c r="R67" s="8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="216.75">
+      <c r="A68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" t="s">
+        <v>288</v>
+      </c>
+      <c r="E68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="H68" t="s">
+        <v>24</v>
+      </c>
+      <c r="J68" s="9">
+        <v>46223</v>
+      </c>
+      <c r="M68" t="s">
+        <v>27</v>
+      </c>
+      <c r="N68" t="s">
+        <v>32</v>
+      </c>
+      <c r="O68" t="s">
+        <v>32</v>
+      </c>
+      <c r="P68" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>27</v>
+      </c>
+      <c r="R68" s="8" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="88.5">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" t="s">
+        <v>292</v>
+      </c>
+      <c r="E69" t="s">
+        <v>21</v>
+      </c>
+      <c r="F69" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="H69" t="s">
+        <v>24</v>
+      </c>
+      <c r="J69" s="9">
+        <v>46227</v>
+      </c>
+      <c r="M69" t="s">
+        <v>27</v>
+      </c>
+      <c r="N69" t="s">
+        <v>32</v>
+      </c>
+      <c r="O69" t="s">
+        <v>32</v>
+      </c>
+      <c r="P69" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>27</v>
+      </c>
+      <c r="R69" s="8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="159">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" t="s">
+        <v>296</v>
+      </c>
+      <c r="E70" t="s">
+        <v>21</v>
+      </c>
+      <c r="F70" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="H70" t="s">
+        <v>24</v>
+      </c>
+      <c r="J70" s="9">
+        <v>46231</v>
+      </c>
+      <c r="M70" t="s">
+        <v>27</v>
+      </c>
+      <c r="N70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O70" t="s">
+        <v>32</v>
+      </c>
+      <c r="P70" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>27</v>
+      </c>
+      <c r="R70" s="8" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -4451,24 +4910,20 @@
     <hyperlink ref="R61" r:id="rId58" xr:uid="{6618B704-9ABB-44A4-987B-DCC3AA25C4F6}"/>
     <hyperlink ref="R60" r:id="rId59" xr:uid="{11F85A23-2D88-4FF9-8C09-AD8BBB775F57}"/>
     <hyperlink ref="R62" r:id="rId60" xr:uid="{7E878AAF-E5A2-4225-9D68-ACA05D584E6E}"/>
+    <hyperlink ref="R63" r:id="rId61" xr:uid="{98D9E517-C23D-458D-9680-FE1BB06A42E4}"/>
+    <hyperlink ref="R65" r:id="rId62" xr:uid="{711B6D07-B4C4-4DAE-8AAA-2E2E2A1DF18F}"/>
+    <hyperlink ref="R67" r:id="rId63" xr:uid="{9D91076F-C2D3-4955-8793-9D0E3A31B627}"/>
+    <hyperlink ref="R66" r:id="rId64" xr:uid="{AA2F098B-ADC2-4310-9345-1C938342A2B5}"/>
+    <hyperlink ref="R68" r:id="rId65" xr:uid="{947D38E4-A486-4A31-A8FB-58619D4D55BF}"/>
+    <hyperlink ref="R69" r:id="rId66" xr:uid="{F720FD0E-9DF8-4865-B2E7-8196656D5ECD}"/>
+    <hyperlink ref="R70" r:id="rId67" xr:uid="{EA865841-DA7D-4DB1-B55B-D4FBE903117B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId61"/>
+  <legacyDrawing r:id="rId68"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="45bfb739-6ba1-455a-9ebc-7c7aad4d3f52" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1ae98369-b7b5-4200-a1f2-aa19ea46d141">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000DA49A99A991BB46895C75ED0BD7DB0A" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ea6ae809972c099a9ea9350c2630a444">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1ae98369-b7b5-4200-a1f2-aa19ea46d141" xmlns:ns3="45bfb739-6ba1-455a-9ebc-7c7aad4d3f52" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ef78da573ebc2149f9ce4278297dbff3" ns2:_="" ns3:_="">
     <xsd:import namespace="1ae98369-b7b5-4200-a1f2-aa19ea46d141"/>
@@ -4675,7 +5130,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4684,14 +5139,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="45bfb739-6ba1-455a-9ebc-7c7aad4d3f52" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1ae98369-b7b5-4200-a1f2-aa19ea46d141">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{036C12ED-DBD6-4014-9301-42952C769E9B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B75C2264-2D83-4225-8EFE-E604E5DB3828}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B75C2264-2D83-4225-8EFE-E604E5DB3828}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D67DC10B-EAB1-4B04-9793-7549042311B4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D67DC10B-EAB1-4B04-9793-7549042311B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{036C12ED-DBD6-4014-9301-42952C769E9B}"/>
 </file>